--- a/server/database/products.xlsx
+++ b/server/database/products.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:K7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,33 +419,18 @@
         <v>category</v>
       </c>
       <c r="G1" t="str">
+        <v>images</v>
+      </c>
+      <c r="H1" t="str">
         <v>stock</v>
       </c>
-      <c r="H1" t="str">
-        <v>images</v>
-      </c>
       <c r="I1" t="str">
-        <v>isTrending</v>
+        <v>ratings</v>
       </c>
       <c r="J1" t="str">
-        <v>isBestSeller</v>
+        <v>reviewsCount</v>
       </c>
       <c r="K1" t="str">
-        <v>isFeatured</v>
-      </c>
-      <c r="L1" t="str">
-        <v>isNewArrival</v>
-      </c>
-      <c r="M1" t="str">
-        <v>limitedOffer</v>
-      </c>
-      <c r="N1" t="str">
-        <v>ratings</v>
-      </c>
-      <c r="O1" t="str">
-        <v>reviews</v>
-      </c>
-      <c r="P1" t="str">
         <v>createdAt</v>
       </c>
     </row>
@@ -468,34 +453,19 @@
       <c r="F2" t="str">
         <v>Rings</v>
       </c>
-      <c r="G2">
+      <c r="G2" t="str">
+        <v>["https://images.unsplash.com/photo-1605100804763-247f67b3557e?w=600&amp;auto=format&amp;fit=crop&amp;q=80","https://images.unsplash.com/photo-1543294001-f7cbfe92237e?w=600&amp;auto=format&amp;fit=crop&amp;q=80"]</v>
+      </c>
+      <c r="H2">
         <v>12</v>
       </c>
-      <c r="H2" t="str">
-        <v>["https://images.unsplash.com/photo-1605100804763-247f67b3557e?w=600&amp;auto=format&amp;fit=crop&amp;q=80","https://images.unsplash.com/photo-1543294001-f7cbfe92237e?w=600&amp;auto=format&amp;fit=crop&amp;q=80"]</v>
-      </c>
-      <c r="I2" t="b">
-        <v>1</v>
-      </c>
-      <c r="J2" t="b">
-        <v>1</v>
-      </c>
-      <c r="K2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L2" t="b">
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="M2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2" t="str">
-        <v>[]</v>
-      </c>
-      <c r="P2" t="str">
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
         <v>2026-07-24T06:14:24.140Z</v>
       </c>
     </row>
@@ -518,34 +488,19 @@
       <c r="F3" t="str">
         <v>Bangles</v>
       </c>
-      <c r="G3">
+      <c r="G3" t="str">
+        <v>["https://images.unsplash.com/photo-1611591437281-460bfbe1220a?w=600&amp;auto=format&amp;fit=crop&amp;q=80","https://images.unsplash.com/photo-1535632066927-ab7c9ab60908?w=600&amp;auto=format&amp;fit=crop&amp;q=80"]</v>
+      </c>
+      <c r="H3">
         <v>24</v>
       </c>
-      <c r="H3" t="str">
-        <v>["https://images.unsplash.com/photo-1611591437281-460bfbe1220a?w=600&amp;auto=format&amp;fit=crop&amp;q=80","https://images.unsplash.com/photo-1535632066927-ab7c9ab60908?w=600&amp;auto=format&amp;fit=crop&amp;q=80"]</v>
-      </c>
-      <c r="I3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J3" t="b">
+      <c r="I3">
         <v>0</v>
       </c>
-      <c r="K3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3" t="str">
-        <v>[]</v>
-      </c>
-      <c r="P3" t="str">
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
         <v>2026-07-24T06:14:24.140Z</v>
       </c>
     </row>
@@ -568,34 +523,19 @@
       <c r="F4" t="str">
         <v>Earrings</v>
       </c>
-      <c r="G4">
+      <c r="G4" t="str">
+        <v>["https://images.unsplash.com/photo-1635767798638-3e25273a8236?w=600&amp;auto=format&amp;fit=crop&amp;q=80"]</v>
+      </c>
+      <c r="H4">
         <v>8</v>
       </c>
-      <c r="H4" t="str">
-        <v>["https://images.unsplash.com/photo-1635767798638-3e25273a8236?w=600&amp;auto=format&amp;fit=crop&amp;q=80"]</v>
-      </c>
-      <c r="I4" t="b">
+      <c r="I4">
         <v>0</v>
       </c>
-      <c r="J4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K4" t="b">
-        <v>1</v>
-      </c>
-      <c r="L4" t="b">
-        <v>1</v>
-      </c>
-      <c r="M4" t="b">
-        <v>1</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4" t="str">
-        <v>[]</v>
-      </c>
-      <c r="P4" t="str">
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
         <v>2026-07-24T06:14:24.140Z</v>
       </c>
     </row>
@@ -616,36 +556,21 @@
         <v>64500</v>
       </c>
       <c r="F5" t="str">
-        <v>Necklaces</v>
-      </c>
-      <c r="G5">
+        <v>Hamper</v>
+      </c>
+      <c r="G5" t="str">
+        <v>["https://images.unsplash.com/photo-1599643478518-a784e5dc4c8f?w=600&amp;auto=format&amp;fit=crop&amp;q=80","https://images.unsplash.com/photo-1617038260897-41a1f14a8ca0?w=600&amp;auto=format&amp;fit=crop&amp;q=80"]</v>
+      </c>
+      <c r="H5">
         <v>15</v>
       </c>
-      <c r="H5" t="str">
-        <v>["https://images.unsplash.com/photo-1599643478518-a784e5dc4c8f?w=600&amp;auto=format&amp;fit=crop&amp;q=80","https://images.unsplash.com/photo-1617038260897-41a1f14a8ca0?w=600&amp;auto=format&amp;fit=crop&amp;q=80"]</v>
-      </c>
-      <c r="I5" t="b">
-        <v>1</v>
-      </c>
-      <c r="J5" t="b">
+      <c r="I5">
         <v>0</v>
       </c>
-      <c r="K5" t="b">
-        <v>0</v>
-      </c>
-      <c r="L5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M5" t="b">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5" t="str">
-        <v>[]</v>
-      </c>
-      <c r="P5" t="str">
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
         <v>2026-07-24T06:14:24.140Z</v>
       </c>
     </row>
@@ -668,34 +593,19 @@
       <c r="F6" t="str">
         <v>Watches</v>
       </c>
-      <c r="G6">
+      <c r="G6" t="str">
+        <v>["https://images.unsplash.com/photo-1523275335684-37898b6baf30?w=600&amp;auto=format&amp;fit=crop&amp;q=80","https://images.unsplash.com/photo-1547996160-81dfa63595aa?w=600&amp;auto=format&amp;fit=crop&amp;q=80"]</v>
+      </c>
+      <c r="H6">
         <v>6</v>
       </c>
-      <c r="H6" t="str">
-        <v>["https://images.unsplash.com/photo-1523275335684-37898b6baf30?w=600&amp;auto=format&amp;fit=crop&amp;q=80","https://images.unsplash.com/photo-1547996160-81dfa63595aa?w=600&amp;auto=format&amp;fit=crop&amp;q=80"]</v>
-      </c>
-      <c r="I6" t="b">
+      <c r="I6">
         <v>0</v>
       </c>
-      <c r="J6" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" t="b">
-        <v>0</v>
-      </c>
-      <c r="L6" t="b">
-        <v>0</v>
-      </c>
-      <c r="M6" t="b">
-        <v>1</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6" t="str">
-        <v>[]</v>
-      </c>
-      <c r="P6" t="str">
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
         <v>2026-07-24T06:14:24.140Z</v>
       </c>
     </row>
@@ -718,40 +628,25 @@
       <c r="F7" t="str">
         <v>Bangles</v>
       </c>
-      <c r="G7">
+      <c r="G7" t="str">
+        <v>["https://images.unsplash.com/photo-1535632066927-ab7c9ab60908?w=600&amp;auto=format&amp;fit=crop&amp;q=80"]</v>
+      </c>
+      <c r="H7">
         <v>30</v>
       </c>
-      <c r="H7" t="str">
-        <v>["https://images.unsplash.com/photo-1535632066927-ab7c9ab60908?w=600&amp;auto=format&amp;fit=crop&amp;q=80"]</v>
-      </c>
-      <c r="I7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J7" t="b">
+      <c r="I7">
         <v>0</v>
       </c>
-      <c r="K7" t="b">
-        <v>1</v>
-      </c>
-      <c r="L7" t="b">
-        <v>1</v>
-      </c>
-      <c r="M7" t="b">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7" t="str">
-        <v>[]</v>
-      </c>
-      <c r="P7" t="str">
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
         <v>2026-07-24T06:14:24.140Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/server/database/products.xlsx
+++ b/server/database/products.xlsx
@@ -486,7 +486,7 @@
         <v>47300</v>
       </c>
       <c r="F3" t="str">
-        <v>Bangles</v>
+        <v>Bracelet</v>
       </c>
       <c r="G3" t="str">
         <v>["https://images.unsplash.com/photo-1611591437281-460bfbe1220a?w=600&amp;auto=format&amp;fit=crop&amp;q=80","https://images.unsplash.com/photo-1535632066927-ab7c9ab60908?w=600&amp;auto=format&amp;fit=crop&amp;q=80"]</v>
@@ -626,7 +626,7 @@
         <v>42914</v>
       </c>
       <c r="F7" t="str">
-        <v>Bangles</v>
+        <v>Bracelet</v>
       </c>
       <c r="G7" t="str">
         <v>["https://images.unsplash.com/photo-1535632066927-ab7c9ab60908?w=600&amp;auto=format&amp;fit=crop&amp;q=80"]</v>
